--- a/output/Data and Chart Outputs/albania_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/albania_power_generation_daily.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Albania power generation by type (ENTSO-E) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -185,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$6</f>
+              <f>'Chart'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -213,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$6</f>
+              <f>'Chart'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -241,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$6</f>
+              <f>'Chart'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -269,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$6</f>
+              <f>'Chart'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -297,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$6</f>
+              <f>'Chart'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -325,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$6</f>
+              <f>'Chart'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -353,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$6</f>
+              <f>'Chart'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -888,7 +889,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03 09:52 UTC; 129 days, 2026-05-27 to 2026-10-02</t>
+          <t>2026-10-28 00:44 UTC; 152 days, 2026-05-27 to 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -903,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -953,10 +954,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" t="n">
-        <v>77.02380000000001</v>
+        <v>436.6807</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -965,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.996600000000001</v>
+        <v>74.25569999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -974,15 +975,15 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.5777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" t="n">
-        <v>436.6807</v>
+        <v>499.32</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -991,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>74.25569999999999</v>
+        <v>95.31979999999999</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1000,15 +1001,15 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5777</v>
+        <v>6.2018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B4" t="n">
-        <v>499.32</v>
+        <v>584.2952</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1017,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>95.3198</v>
+        <v>87.15099999999998</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1026,15 +1027,15 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2018</v>
+        <v>17.8599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B5" t="n">
-        <v>584.2951999999999</v>
+        <v>264.2551</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1043,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>87.151</v>
+        <v>69.6392</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1052,32 +1053,6 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17.8599</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B6" t="n">
-        <v>264.2551</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>69.6392</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1093,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P130"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7583,7 +7558,7 @@
         <v>46297</v>
       </c>
       <c r="B130" t="n">
-        <v>8623.6</v>
+        <v>9156.4</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -7616,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>11110.5</v>
+        <v>11643.3</v>
       </c>
       <c r="N130" t="n">
         <v>0</v>
@@ -7626,6 +7601,1156 @@
       </c>
       <c r="P130" t="n">
         <v>18447.8</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B131" t="n">
+        <v>9353</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2548</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>11901.1</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>18354.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B132" t="n">
+        <v>6616.1</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>2459.2</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>9075.299999999999</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>17808.4</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B133" t="n">
+        <v>10577</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>2527.7</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>13104.8</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>18618</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B134" t="n">
+        <v>10210.1</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>3690.6</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>13900.7</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>18765.9</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B135" t="n">
+        <v>10027.3</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>3731.5</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>13758.9</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>18812.3</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B136" t="n">
+        <v>11653.2</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2220.4</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>13873.6</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>19981</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B137" t="n">
+        <v>13964</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>200.8</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>14164.8</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>20608.1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B138" t="n">
+        <v>12862.1</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1249.6</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>14111.8</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>20136.8</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B139" t="n">
+        <v>9388.799999999999</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2342.4</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>11731.1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>19147.2</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B140" t="n">
+        <v>14341.8</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>2869.7</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>17211.5</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>19401.8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B141" t="n">
+        <v>16341.4</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1648.4</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>17989.8</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>20460.2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B142" t="n">
+        <v>7510.1</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>3613.9</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>11124</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>20008</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B143" t="n">
+        <v>9852.6</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>3184.1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>13036.7</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>20249.6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B144" t="n">
+        <v>8949.299999999999</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>3013.1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>11962.4</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>20263.9</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B145" t="n">
+        <v>9669.4</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>3556.8</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>13226.2</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>20625.8</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B146" t="n">
+        <v>7145.4</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>2984.4</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>10129.8</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>20035.6</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B147" t="n">
+        <v>8742.5</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>3399.6</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>12142.1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>20476.5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B148" t="n">
+        <v>8660</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>3258.4</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>11918.5</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>20126.3</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B149" t="n">
+        <v>10604.6</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1322.6</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>11927.2</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>21643.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B150" t="n">
+        <v>7255.8</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>3027.2</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>10283.1</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>20170.9</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B151" t="n">
+        <v>7494.3</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>3287.9</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>10782.2</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>19882.8</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B152" t="n">
+        <v>8037.4</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>2840.6</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>10878</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>19030.2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B153" t="n">
+        <v>10176.6</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>2187.7</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>12364.3</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>21272.7</v>
       </c>
     </row>
   </sheetData>
